--- a/schoolDocs/StudentImportData/UKG_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/UKG_ImportReady.xlsx
@@ -673,27 +673,27 @@
   <dimension ref="A1:U15"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="32.992" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="25.708" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="17.567" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="10" max="10" width="24.565" bestFit="true" customWidth="true" style="0"/>
-    <col min="11" max="11" width="29.279" bestFit="true" customWidth="true" style="0"/>
-    <col min="12" max="12" width="35.277" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="14" max="14" width="26.993" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="16" max="16" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="17" max="17" width="16.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="18" max="18" width="23.423" bestFit="true" customWidth="true" style="0"/>
-    <col min="19" max="19" width="15.139" bestFit="true" customWidth="true" style="0"/>
-    <col min="20" max="20" width="22.28" bestFit="true" customWidth="true" style="0"/>
-    <col min="21" max="21" width="101.404" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" customWidth="true" style="0"/>
+    <col min="2" max="2" width="32.992" customWidth="true" style="0"/>
+    <col min="3" max="3" width="18.71" customWidth="true" style="0"/>
+    <col min="4" max="4" width="10.426" customWidth="true" style="0"/>
+    <col min="5" max="5" width="10.569" customWidth="true" style="0"/>
+    <col min="6" max="6" width="11.569" customWidth="true" style="0"/>
+    <col min="7" max="7" width="25.708" customWidth="true" style="0"/>
+    <col min="8" max="8" width="17.567" customWidth="true" style="0"/>
+    <col min="9" max="9" width="15.139" customWidth="true" style="0"/>
+    <col min="10" max="10" width="24.565" customWidth="true" style="0"/>
+    <col min="11" max="11" width="29.279" customWidth="true" style="0"/>
+    <col min="12" max="12" width="35.277" customWidth="true" style="0"/>
+    <col min="13" max="13" width="15.282" customWidth="true" style="0"/>
+    <col min="14" max="14" width="26.993" customWidth="true" style="0"/>
+    <col min="15" max="15" width="16.282" customWidth="true" style="0"/>
+    <col min="16" max="16" width="28.136" customWidth="true" style="0"/>
+    <col min="17" max="17" width="16.282" customWidth="true" style="0"/>
+    <col min="18" max="18" width="23.423" customWidth="true" style="0"/>
+    <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
+    <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
+    <col min="21" max="21" width="101.404" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -786,6 +786,7 @@
       <c r="I2">
         <v>50</v>
       </c>
+      <c r="J2"/>
       <c r="K2">
         <v>8100</v>
       </c>
@@ -827,6 +828,11 @@
       <c r="H3" t="s">
         <v>32</v>
       </c>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3">
+        <v>16200</v>
+      </c>
       <c r="L3" t="s">
         <v>33</v>
       </c>
@@ -862,8 +868,10 @@
       <c r="H4" t="s">
         <v>32</v>
       </c>
+      <c r="I4"/>
+      <c r="J4"/>
       <c r="K4">
-        <v>5400</v>
+        <v>8000</v>
       </c>
       <c r="L4" t="s">
         <v>38</v>
@@ -898,6 +906,8 @@
       <c r="H5" t="s">
         <v>43</v>
       </c>
+      <c r="I5"/>
+      <c r="J5"/>
       <c r="K5">
         <v>16200</v>
       </c>
@@ -933,6 +943,11 @@
       <c r="H6" t="s">
         <v>49</v>
       </c>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6">
+        <v>0</v>
+      </c>
       <c r="L6" t="s">
         <v>50</v>
       </c>
@@ -971,6 +986,10 @@
       <c r="I7">
         <v>50</v>
       </c>
+      <c r="J7"/>
+      <c r="K7">
+        <v>6100</v>
+      </c>
       <c r="L7" t="s">
         <v>54</v>
       </c>
@@ -1009,6 +1028,11 @@
       <c r="H8" t="s">
         <v>32</v>
       </c>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8">
+        <v>12200</v>
+      </c>
       <c r="L8" t="s">
         <v>38</v>
       </c>
@@ -1041,8 +1065,9 @@
       <c r="I9">
         <v>30</v>
       </c>
+      <c r="J9"/>
       <c r="K9" s="5">
-        <v>3000</v>
+        <v>8540</v>
       </c>
       <c r="L9" t="s">
         <v>60</v>
@@ -1085,6 +1110,11 @@
       <c r="H10" t="s">
         <v>49</v>
       </c>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10">
+        <v>0</v>
+      </c>
       <c r="L10" t="s">
         <v>65</v>
       </c>
@@ -1126,8 +1156,12 @@
       <c r="H11" t="s">
         <v>25</v>
       </c>
+      <c r="I11"/>
       <c r="J11">
         <v>1200</v>
+      </c>
+      <c r="K11">
+        <v>1200.0</v>
       </c>
       <c r="L11" t="s">
         <v>70</v>
@@ -1171,8 +1205,10 @@
       <c r="H12" t="s">
         <v>32</v>
       </c>
+      <c r="I12"/>
+      <c r="J12"/>
       <c r="K12" s="5">
-        <v>8200</v>
+        <v>12200</v>
       </c>
       <c r="L12" t="s">
         <v>75</v>
@@ -1209,6 +1245,8 @@
       <c r="H13" t="s">
         <v>32</v>
       </c>
+      <c r="I13"/>
+      <c r="J13"/>
       <c r="K13">
         <v>12200</v>
       </c>
@@ -1238,6 +1276,8 @@
       <c r="H14" t="s">
         <v>32</v>
       </c>
+      <c r="I14"/>
+      <c r="J14"/>
       <c r="K14">
         <v>12200</v>
       </c>
@@ -1272,6 +1312,11 @@
       </c>
       <c r="H15" t="s">
         <v>49</v>
+      </c>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15">
+        <v>0</v>
       </c>
       <c r="L15" t="s">
         <v>86</v>

--- a/schoolDocs/StudentImportData/UKG_ImportReady.xlsx
+++ b/schoolDocs/StudentImportData/UKG_ImportReady.xlsx
@@ -14,8 +14,34 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="U1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <rFont val="Calibri"/>
+            <b val="false"/>
+            <i val="false"/>
+            <strike val="false"/>
+            <color rgb="FF000000"/>
+            <sz val="11"/>
+            <u val="none"/>
+          </rPr>
+          <t xml:space="preserve">Only for RTE students. Alphanumeric, e.g. 26MS011157 (Year+StateCode+Sequence). Leave blank for non-RTE.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="82">
   <si>
     <t>Sr No</t>
   </si>
@@ -77,7 +103,7 @@
     <t>DGA Admission No</t>
   </si>
   <si>
-    <t>Notes for Verification (ignored on import)</t>
+    <t>RTE Application No</t>
   </si>
   <si>
     <t>Devansh Kiran Jamdar</t>
@@ -107,9 +133,6 @@
     <t>Worker at Sayadri</t>
   </si>
   <si>
-    <t>Discount 50% on boys fee ₹16200 = ₹8100 payable</t>
-  </si>
-  <si>
     <t>Prithviraj Prashanta Dudhal</t>
   </si>
   <si>
@@ -140,9 +163,6 @@
     <t>1.5km</t>
   </si>
   <si>
-    <t>Class column was blank — assumed UKG, please verify.</t>
-  </si>
-  <si>
     <t>Ganesh Santosh Lokhande</t>
   </si>
   <si>
@@ -158,9 +178,6 @@
     <t>19km</t>
   </si>
   <si>
-    <t>CoC student — ₹16200 collected</t>
-  </si>
-  <si>
     <t>Rajratna Somnath Thorat</t>
   </si>
   <si>
@@ -170,7 +187,7 @@
     <t>12/12/2022</t>
   </si>
   <si>
-    <t>RTE — fees paid by government</t>
+    <t>25MS000003</t>
   </si>
   <si>
     <t>Mahi Somnath Dede</t>
@@ -188,9 +205,6 @@
     <t>Home-maker</t>
   </si>
   <si>
-    <t>Discount 50% on girls fee ₹12200 = ₹6100 payable — collected ₹0</t>
-  </si>
-  <si>
     <t>Aaradhya Lakshman Magar</t>
   </si>
   <si>
@@ -206,9 +220,6 @@
     <t>Home maker</t>
   </si>
   <si>
-    <t>Discount 30% on girls ₹12200 = ₹8540 payable — collected ₹3000 (partial)</t>
-  </si>
-  <si>
     <t>Anvi Rahul Rupanavar</t>
   </si>
   <si>
@@ -224,6 +235,9 @@
     <t>Dabba service</t>
   </si>
   <si>
+    <t>25MS000004</t>
+  </si>
+  <si>
     <t>Hawabi Firoz Saiyed</t>
   </si>
   <si>
@@ -236,9 +250,6 @@
     <t>Brick Worker</t>
   </si>
   <si>
-    <t>90% of ₹12200 = ₹1220 but DGA shows ₹1200 — using ₹1200 as custom fee. Please verify.</t>
-  </si>
-  <si>
     <t>Srinidhi Sachin Dolare</t>
   </si>
   <si>
@@ -251,9 +262,6 @@
     <t>500meter</t>
   </si>
   <si>
-    <t>Partial — ₹8200 of ₹12200 collected</t>
-  </si>
-  <si>
     <t>Ishanvi Deepak Nithnavre</t>
   </si>
   <si>
@@ -276,6 +284,9 @@
   </si>
   <si>
     <t>24/01/2024</t>
+  </si>
+  <si>
+    <t>25MS000005</t>
   </si>
 </sst>
 </file>
@@ -327,12 +338,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF7B3F00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
@@ -340,6 +345,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5EAD0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E4057"/>
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
@@ -361,16 +372,16 @@
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="0" fillId="4" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="5" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -693,7 +704,7 @@
     <col min="18" max="18" width="23.423" customWidth="true" style="0"/>
     <col min="19" max="19" width="15.139" customWidth="true" style="0"/>
     <col min="20" max="20" width="22.28" customWidth="true" style="0"/>
-    <col min="21" max="21" width="101.404" customWidth="true" style="0"/>
+    <col min="21" max="21" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" customHeight="1" ht="30">
@@ -727,10 +738,10 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="1" t="s">
@@ -757,7 +768,7 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -802,16 +813,14 @@
       <c r="P2" t="s">
         <v>29</v>
       </c>
-      <c r="U2" t="s">
-        <v>30</v>
-      </c>
+      <c r="U2"/>
     </row>
     <row r="3" spans="1:21">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
         <v>22</v>
@@ -826,7 +835,7 @@
         <v>9730253332</v>
       </c>
       <c r="H3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I3"/>
       <c r="J3"/>
@@ -834,24 +843,25 @@
         <v>16200</v>
       </c>
       <c r="L3" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" t="s">
         <v>33</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>34</v>
       </c>
-      <c r="N3" t="s">
+      <c r="P3" t="s">
         <v>35</v>
       </c>
-      <c r="P3" t="s">
-        <v>36</v>
-      </c>
+      <c r="U3"/>
     </row>
     <row r="4" spans="1:21">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -866,7 +876,7 @@
         <v>8261843501</v>
       </c>
       <c r="H4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4"/>
       <c r="J4"/>
@@ -874,25 +884,23 @@
         <v>8000</v>
       </c>
       <c r="L4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" t="s">
         <v>38</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>39</v>
       </c>
-      <c r="N4" t="s">
-        <v>40</v>
-      </c>
-      <c r="T4" s="5"/>
-      <c r="U4" t="s">
-        <v>41</v>
-      </c>
+      <c r="T4" s="4"/>
+      <c r="U4"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -904,7 +912,7 @@
         <v>24</v>
       </c>
       <c r="H5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I5"/>
       <c r="J5"/>
@@ -912,24 +920,22 @@
         <v>16200</v>
       </c>
       <c r="L5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
         <v>44</v>
       </c>
-      <c r="M5" t="s">
-        <v>45</v>
-      </c>
-      <c r="N5" t="s">
-        <v>46</v>
-      </c>
-      <c r="U5" t="s">
-        <v>47</v>
-      </c>
+      <c r="U5"/>
     </row>
     <row r="6" spans="1:21">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -941,7 +947,7 @@
         <v>24</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I6"/>
       <c r="J6"/>
@@ -949,16 +955,16 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M6" t="s">
+        <v>33</v>
+      </c>
+      <c r="N6" t="s">
         <v>34</v>
       </c>
-      <c r="N6" t="s">
-        <v>35</v>
-      </c>
       <c r="U6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -966,10 +972,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>23</v>
@@ -991,33 +997,31 @@
         <v>6100</v>
       </c>
       <c r="L7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M7" t="s">
+        <v>33</v>
+      </c>
+      <c r="N7" t="s">
         <v>34</v>
       </c>
-      <c r="N7" t="s">
-        <v>35</v>
-      </c>
       <c r="P7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R7" t="s">
-        <v>56</v>
-      </c>
-      <c r="U7" t="s">
-        <v>57</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="U7"/>
     </row>
     <row r="8" spans="1:21">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>23</v>
@@ -1026,7 +1030,7 @@
         <v>24</v>
       </c>
       <c r="H8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I8"/>
       <c r="J8"/>
@@ -1034,21 +1038,22 @@
         <v>12200</v>
       </c>
       <c r="L8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P8" t="s">
         <v>29</v>
       </c>
+      <c r="U8"/>
     </row>
     <row r="9" spans="1:21">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
@@ -1066,37 +1071,35 @@
         <v>30</v>
       </c>
       <c r="J9"/>
-      <c r="K9" s="5">
+      <c r="K9" s="4">
         <v>8540</v>
       </c>
       <c r="L9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="M9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N9" t="s">
         <v>39</v>
       </c>
-      <c r="N9" t="s">
-        <v>40</v>
-      </c>
       <c r="P9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="R9" t="s">
-        <v>62</v>
-      </c>
-      <c r="U9" t="s">
-        <v>63</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="U9"/>
     </row>
     <row r="10" spans="1:21">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
         <v>23</v>
@@ -1108,7 +1111,7 @@
         <v>9697026464</v>
       </c>
       <c r="H10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I10"/>
       <c r="J10"/>
@@ -1116,22 +1119,22 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="M10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="N10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="R10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="U10" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1139,10 +1142,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
@@ -1164,7 +1167,7 @@
         <v>1200.0</v>
       </c>
       <c r="L11" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M11" t="s">
         <v>27</v>
@@ -1173,25 +1176,23 @@
         <v>28</v>
       </c>
       <c r="P11" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="R11" t="s">
-        <v>72</v>
-      </c>
-      <c r="T11" s="5"/>
-      <c r="U11" t="s">
-        <v>73</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="T11" s="4"/>
+      <c r="U11"/>
     </row>
     <row r="12" spans="1:21">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
         <v>23</v>
@@ -1203,35 +1204,33 @@
         <v>9834525461</v>
       </c>
       <c r="H12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12"/>
       <c r="J12"/>
-      <c r="K12" s="5">
+      <c r="K12" s="4">
         <v>12200</v>
       </c>
       <c r="L12" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="M12" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="N12" t="s">
-        <v>77</v>
-      </c>
-      <c r="U12" t="s">
-        <v>78</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="U12"/>
     </row>
     <row r="13" spans="1:21">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
@@ -1243,7 +1242,7 @@
         <v>7058493849</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I13"/>
       <c r="J13"/>
@@ -1251,18 +1250,19 @@
         <v>12200</v>
       </c>
       <c r="L13" t="s">
-        <v>80</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="U13"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
         <v>23</v>
@@ -1274,7 +1274,7 @@
         <v>8082007650</v>
       </c>
       <c r="H14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I14"/>
       <c r="J14"/>
@@ -1282,24 +1282,25 @@
         <v>12200</v>
       </c>
       <c r="L14" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="M14" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="N14" t="s">
-        <v>84</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="U14"/>
     </row>
     <row r="15" spans="1:21">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E15" t="s">
         <v>23</v>
@@ -1311,7 +1312,7 @@
         <v>7559241731</v>
       </c>
       <c r="H15" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I15"/>
       <c r="J15"/>
@@ -1319,16 +1320,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="M15" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="N15" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="U15" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1343,6 +1344,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <legacyDrawing r:id="rId_comments_vml1"/>
   <tableParts count="0"/>
 </worksheet>
 </file>